--- a/ksoft/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
+++ b/ksoft/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
@@ -5582,13 +5582,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72A77AD-47C4-4D67-9AFE-ADA8A156C9B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F72AF6C-95D6-4205-9799-238E9B426DC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA9AC52D-EA49-4325-B141-7C2FA498B067}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{158135FE-4B32-4652-8751-C4528163E02B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC3D5A1B-25FC-4E7C-B928-5DAADF0FD45D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A1EAC6-B7D8-468B-A2D3-10DCBB1E0410}"/>
 </file>
--- a/ksoft/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
+++ b/ksoft/docs/records/Operation_Code_No_Finance_Mov_Records.xlsx
@@ -5582,13 +5582,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F72AF6C-95D6-4205-9799-238E9B426DC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E72A77AD-47C4-4D67-9AFE-ADA8A156C9B1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{158135FE-4B32-4652-8751-C4528163E02B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA9AC52D-EA49-4325-B141-7C2FA498B067}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46A1EAC6-B7D8-468B-A2D3-10DCBB1E0410}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC3D5A1B-25FC-4E7C-B928-5DAADF0FD45D}"/>
 </file>